--- a/output/yearly_benthic_cover_iteration_36_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_36_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.64928302601693</v>
+        <v>45.71850773357846</v>
       </c>
       <c r="M2" t="n">
-        <v>99.05421715535041</v>
+        <v>98.92452006906322</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.06888060637949</v>
+        <v>88.08171204887398</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93858045379294</v>
+        <v>45.927047645345</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228829708138568</v>
+        <v>2.228871335197796</v>
       </c>
       <c r="E3" t="n">
-        <v>5.714306847423551</v>
+        <v>5.708489758060138</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429432360461894</v>
+        <v>0.7429571117325987</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97611723552813</v>
+        <v>33.97196513124817</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17538885812471</v>
+        <v>34.17602713969953</v>
       </c>
       <c r="I3" t="n">
-        <v>6.58789949582966</v>
+        <v>6.609919624607</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643395225288684</v>
+        <v>4.643481948328741</v>
       </c>
       <c r="K3" t="n">
-        <v>11.93111939362052</v>
+        <v>11.91828795112602</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89383885734181</v>
+        <v>48.91741716470547</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7635387047553</v>
+        <v>106.7627527611765</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.17202559933614</v>
+        <v>87.20428161921677</v>
       </c>
       <c r="C4" t="n">
-        <v>42.68032806118054</v>
+        <v>42.69289729888803</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18573272432384</v>
+        <v>2.186811130175195</v>
       </c>
       <c r="E4" t="n">
-        <v>6.520725037831867</v>
+        <v>6.520748379165761</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445061519744974</v>
+        <v>0.7445247107608945</v>
       </c>
       <c r="G4" t="n">
-        <v>33.31914996286478</v>
+        <v>33.33089276611134</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24728299082687</v>
+        <v>34.24813669500114</v>
       </c>
       <c r="I4" t="n">
-        <v>5.501465281673665</v>
+        <v>5.519888495746843</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653163449840608</v>
+        <v>4.653279442255591</v>
       </c>
       <c r="K4" t="n">
-        <v>12.82797440066388</v>
+        <v>12.79571838078321</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30870032993811</v>
+        <v>44.32777544186744</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81700279178251</v>
+        <v>99.8163911215387</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.09442106386078</v>
+        <v>86.14327278281036</v>
       </c>
       <c r="C5" t="n">
-        <v>42.4566017417521</v>
+        <v>42.4886193297716</v>
       </c>
       <c r="D5" t="n">
-        <v>2.13347394116487</v>
+        <v>2.135419113697199</v>
       </c>
       <c r="E5" t="n">
-        <v>7.130271809956257</v>
+        <v>7.135523172651792</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458300078848994</v>
+        <v>0.7458522863612786</v>
       </c>
       <c r="G5" t="n">
-        <v>32.52252089034668</v>
+        <v>32.54758698966549</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30818036270536</v>
+        <v>34.30920517261881</v>
       </c>
       <c r="I5" t="n">
-        <v>4.592706502522091</v>
+        <v>4.608109258057802</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66143754928062</v>
+        <v>4.661576789757991</v>
       </c>
       <c r="K5" t="n">
-        <v>13.90557893613921</v>
+        <v>13.85672721718964</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48500084206221</v>
+        <v>43.50132321704577</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84718151995351</v>
+        <v>99.846669764007</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.85342096303138</v>
+        <v>84.94624189077227</v>
       </c>
       <c r="C6" t="n">
-        <v>41.92897245165135</v>
+        <v>42.00736584506792</v>
       </c>
       <c r="D6" t="n">
-        <v>2.07322947417576</v>
+        <v>2.077424403815033</v>
       </c>
       <c r="E6" t="n">
-        <v>7.567765479155294</v>
+        <v>7.582714351400304</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469530347144727</v>
+        <v>0.7469778857319279</v>
       </c>
       <c r="G6" t="n">
-        <v>31.60415863694537</v>
+        <v>31.66364441711721</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35983959686574</v>
+        <v>34.36098274366868</v>
       </c>
       <c r="I6" t="n">
-        <v>3.833018274209284</v>
+        <v>3.845886303214574</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668456466965454</v>
+        <v>4.668611785824549</v>
       </c>
       <c r="K6" t="n">
-        <v>15.14657903696864</v>
+        <v>15.05375810922772</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79687333075439</v>
+        <v>42.8108730107583</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87242481937437</v>
+        <v>99.87199696505394</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.44598538368636</v>
+        <v>83.6062785128631</v>
       </c>
       <c r="C7" t="n">
-        <v>41.11703469484162</v>
+        <v>41.26494855560178</v>
       </c>
       <c r="D7" t="n">
-        <v>2.005041626075589</v>
+        <v>2.012633618132664</v>
       </c>
       <c r="E7" t="n">
-        <v>7.851907900959471</v>
+        <v>7.881058662732983</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479073254960615</v>
+        <v>0.7479335780138429</v>
       </c>
       <c r="G7" t="n">
-        <v>30.56470806221992</v>
+        <v>30.67611755665254</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40373697281883</v>
+        <v>34.40494458863677</v>
       </c>
       <c r="I7" t="n">
-        <v>3.198262711766102</v>
+        <v>3.209005646107799</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674420784350384</v>
+        <v>4.674584862586517</v>
       </c>
       <c r="K7" t="n">
-        <v>16.55401461631365</v>
+        <v>16.39372148713688</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22247795900559</v>
+        <v>42.23449978217204</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89352727016086</v>
+        <v>99.89316982491071</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.32688557284131</v>
+        <v>88.39544953994724</v>
       </c>
       <c r="C8" t="n">
-        <v>43.42863894021706</v>
+        <v>43.51877317577306</v>
       </c>
       <c r="D8" t="n">
-        <v>2.009312556568775</v>
+        <v>2.01690046611494</v>
       </c>
       <c r="E8" t="n">
-        <v>9.691465123567676</v>
+        <v>9.680566095209432</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495004396543899</v>
+        <v>0.7495192212474014</v>
       </c>
       <c r="G8" t="n">
-        <v>31.07086797634517</v>
+        <v>31.16404859158495</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47702022410193</v>
+        <v>34.47788417738046</v>
       </c>
       <c r="I8" t="n">
-        <v>5.644341504763436</v>
+        <v>5.622035855613796</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684377747839936</v>
+        <v>4.684495132796259</v>
       </c>
       <c r="K8" t="n">
-        <v>11.67311442715869</v>
+        <v>11.60455046005277</v>
       </c>
       <c r="L8" t="n">
-        <v>44.71050183019021</v>
+        <v>44.68967162504671</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81225519756596</v>
+        <v>99.81299526087255</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.50202703591575</v>
+        <v>86.51457887929963</v>
       </c>
       <c r="C9" t="n">
-        <v>42.48022387931652</v>
+        <v>42.5110020267888</v>
       </c>
       <c r="D9" t="n">
-        <v>1.927077822241592</v>
+        <v>1.931881063858764</v>
       </c>
       <c r="E9" t="n">
-        <v>10.08018426902285</v>
+        <v>10.05474676288531</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508613962470928</v>
+        <v>0.7508746267400324</v>
       </c>
       <c r="G9" t="n">
-        <v>29.79923675849572</v>
+        <v>29.85037504762336</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53962422736627</v>
+        <v>34.54023283004148</v>
       </c>
       <c r="I9" t="n">
-        <v>4.712158835997897</v>
+        <v>4.693502131025483</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69288372654433</v>
+        <v>4.692966417125201</v>
       </c>
       <c r="K9" t="n">
-        <v>13.49797296408422</v>
+        <v>13.48542112070038</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86501589257807</v>
+        <v>43.84740918985488</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84321273597882</v>
+        <v>99.84383233734405</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.36393331314065</v>
+        <v>84.51632057043726</v>
       </c>
       <c r="C10" t="n">
-        <v>41.07373302823184</v>
+        <v>41.24149448822085</v>
       </c>
       <c r="D10" t="n">
-        <v>1.831363438994614</v>
+        <v>1.84245091093947</v>
       </c>
       <c r="E10" t="n">
-        <v>10.23500371012512</v>
+        <v>10.24217738532444</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520281916842997</v>
+        <v>0.7520347171237601</v>
       </c>
       <c r="G10" t="n">
-        <v>28.31916390692174</v>
+        <v>28.46854898433815</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59329681747779</v>
+        <v>34.59359698769296</v>
       </c>
       <c r="I10" t="n">
-        <v>3.932901049910219</v>
+        <v>3.917294602994976</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700176198026872</v>
+        <v>4.7002169820235</v>
       </c>
       <c r="K10" t="n">
-        <v>15.63606668685934</v>
+        <v>15.48367942956276</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15930698390885</v>
+        <v>43.14445102302125</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86910669900003</v>
+        <v>99.86962494080485</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.10278441044044</v>
+        <v>82.4336572766521</v>
       </c>
       <c r="C11" t="n">
-        <v>39.42264660195754</v>
+        <v>39.76661739880111</v>
       </c>
       <c r="D11" t="n">
-        <v>1.731130546459004</v>
+        <v>1.750139563360478</v>
       </c>
       <c r="E11" t="n">
-        <v>10.22179275915289</v>
+        <v>10.2738067897569</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530301854481157</v>
+        <v>0.7530287270227232</v>
       </c>
       <c r="G11" t="n">
-        <v>26.76921939446652</v>
+        <v>27.0422042688511</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63938853061332</v>
+        <v>34.63932144304526</v>
       </c>
       <c r="I11" t="n">
-        <v>3.281784335249865</v>
+        <v>3.26872694072363</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706438659050723</v>
+        <v>4.706429543892019</v>
       </c>
       <c r="K11" t="n">
-        <v>17.89721558955956</v>
+        <v>17.56634272334789</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57089055709651</v>
+        <v>42.55822613887894</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89075274861361</v>
+        <v>99.89118626102794</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.69266032597795</v>
+        <v>80.28751300900356</v>
       </c>
       <c r="C12" t="n">
-        <v>37.52085218095985</v>
+        <v>38.12702493422093</v>
       </c>
       <c r="D12" t="n">
-        <v>1.625241510418356</v>
+        <v>1.655866253888302</v>
       </c>
       <c r="E12" t="n">
-        <v>10.05287598271583</v>
+        <v>10.17490005649608</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538925654414577</v>
+        <v>0.7538812991033385</v>
       </c>
       <c r="G12" t="n">
-        <v>25.13181149184546</v>
+        <v>25.58554438570891</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67905801030705</v>
+        <v>34.67853975875357</v>
       </c>
       <c r="I12" t="n">
-        <v>2.737952231240689</v>
+        <v>2.727023135657492</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71182853400911</v>
+        <v>4.711758119395865</v>
       </c>
       <c r="K12" t="n">
-        <v>20.30733967402205</v>
+        <v>19.71248699099644</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08064746903894</v>
+        <v>42.06969010420698</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90883932402085</v>
+        <v>99.90920202942435</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.2017936404762</v>
+        <v>78.01755098765538</v>
       </c>
       <c r="C13" t="n">
-        <v>35.45322600814721</v>
+        <v>36.27898318713423</v>
       </c>
       <c r="D13" t="n">
-        <v>1.516758332419203</v>
+        <v>1.556920316067769</v>
       </c>
       <c r="E13" t="n">
-        <v>9.762503113007808</v>
+        <v>9.946022374103389</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546359841494472</v>
+        <v>0.7546139867323324</v>
       </c>
       <c r="G13" t="n">
-        <v>23.45428925159133</v>
+        <v>24.05668559174039</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71325527087458</v>
+        <v>34.71224338968729</v>
       </c>
       <c r="I13" t="n">
-        <v>2.283876787499788</v>
+        <v>2.274727912247148</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716474900934045</v>
+        <v>4.716337417077077</v>
       </c>
       <c r="K13" t="n">
-        <v>22.79820635952381</v>
+        <v>21.98244901234461</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6725134036834</v>
+        <v>41.66281715786401</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92394577135443</v>
+        <v>99.92424935734286</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.73530724392675</v>
+        <v>84.37787093383332</v>
       </c>
       <c r="C14" t="n">
-        <v>39.57092058463918</v>
+        <v>40.18711889720198</v>
       </c>
       <c r="D14" t="n">
-        <v>1.518472038606292</v>
+        <v>1.558751933181826</v>
       </c>
       <c r="E14" t="n">
-        <v>12.05372704084543</v>
+        <v>12.14460255606006</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554886080166744</v>
+        <v>0.7555017417949015</v>
       </c>
       <c r="G14" t="n">
-        <v>25.28794201792208</v>
+        <v>25.77554023970388</v>
       </c>
       <c r="H14" t="n">
-        <v>36.55962895609864</v>
+        <v>36.44363361947929</v>
       </c>
       <c r="I14" t="n">
-        <v>2.838244782333423</v>
+        <v>2.977954957395248</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721803800104214</v>
+        <v>4.721885886218134</v>
       </c>
       <c r="K14" t="n">
-        <v>16.26469275607325</v>
+        <v>15.62212906616667</v>
       </c>
       <c r="L14" t="n">
-        <v>44.06988527206852</v>
+        <v>44.09160351327739</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90549861278093</v>
+        <v>99.90085147664604</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.83004750331781</v>
+        <v>83.67738412937619</v>
       </c>
       <c r="C15" t="n">
-        <v>39.10457062899452</v>
+        <v>39.9475145214773</v>
       </c>
       <c r="D15" t="n">
-        <v>1.484511737073518</v>
+        <v>1.532609585436146</v>
       </c>
       <c r="E15" t="n">
-        <v>12.17872425404602</v>
+        <v>12.35493551960812</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562083899281388</v>
+        <v>0.7562493473876697</v>
       </c>
       <c r="G15" t="n">
-        <v>24.72238261726288</v>
+        <v>25.3432500709253</v>
       </c>
       <c r="H15" t="n">
-        <v>36.59446066544967</v>
+        <v>36.47969636137316</v>
       </c>
       <c r="I15" t="n">
-        <v>2.367457402506731</v>
+        <v>2.48408482347286</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726302437050867</v>
+        <v>4.726558421172935</v>
       </c>
       <c r="K15" t="n">
-        <v>17.16995249668219</v>
+        <v>16.32261587062381</v>
       </c>
       <c r="L15" t="n">
-        <v>43.64663674148071</v>
+        <v>43.64714863686012</v>
       </c>
       <c r="M15" t="n">
-        <v>99.9211598671574</v>
+        <v>99.91727902896123</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.29638248062875</v>
+        <v>81.31068493874841</v>
       </c>
       <c r="C16" t="n">
-        <v>36.93697550374745</v>
+        <v>37.96535711376735</v>
       </c>
       <c r="D16" t="n">
-        <v>1.387662173517056</v>
+        <v>1.441374135530265</v>
       </c>
       <c r="E16" t="n">
-        <v>11.71326718445084</v>
+        <v>11.9647574625261</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568282319520143</v>
+        <v>0.756891665286455</v>
       </c>
       <c r="G16" t="n">
-        <v>23.10949407838352</v>
+        <v>23.83457960176592</v>
       </c>
       <c r="H16" t="n">
-        <v>36.62445608055431</v>
+        <v>36.51068027163517</v>
       </c>
       <c r="I16" t="n">
-        <v>1.974498282070927</v>
+        <v>2.071828893964168</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730176449700089</v>
+        <v>4.730572908040344</v>
       </c>
       <c r="K16" t="n">
-        <v>19.70361751937123</v>
+        <v>18.6893150612516</v>
       </c>
       <c r="L16" t="n">
-        <v>43.29364427125615</v>
+        <v>43.27632546877348</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93423729437482</v>
+        <v>99.93099764379241</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.87336381796042</v>
+        <v>82.8145358895907</v>
       </c>
       <c r="C17" t="n">
-        <v>38.10038506421226</v>
+        <v>39.07048996967661</v>
       </c>
       <c r="D17" t="n">
-        <v>1.388764297179959</v>
+        <v>1.442575978997398</v>
       </c>
       <c r="E17" t="n">
-        <v>12.45215271412438</v>
+        <v>12.68425533264711</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574293280394525</v>
+        <v>0.7575227750592952</v>
       </c>
       <c r="G17" t="n">
-        <v>23.5322992138739</v>
+        <v>24.2187135544949</v>
       </c>
       <c r="H17" t="n">
-        <v>37.05799521147246</v>
+        <v>36.9053837832339</v>
       </c>
       <c r="I17" t="n">
-        <v>1.950789753023699</v>
+        <v>2.071567121037496</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733933300246577</v>
+        <v>4.734517344120595</v>
       </c>
       <c r="K17" t="n">
-        <v>18.12663618203958</v>
+        <v>17.18546411040929</v>
       </c>
       <c r="L17" t="n">
-        <v>43.70800403355379</v>
+        <v>43.67505121156482</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93502527980563</v>
+        <v>99.93100529165073</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.4501355945221</v>
+        <v>80.5319528422628</v>
       </c>
       <c r="C18" t="n">
-        <v>35.97836035103267</v>
+        <v>37.10820224957045</v>
       </c>
       <c r="D18" t="n">
-        <v>1.299605109374536</v>
+        <v>1.357674334225904</v>
       </c>
       <c r="E18" t="n">
-        <v>11.92384779086836</v>
+        <v>12.22565711329445</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579462818596518</v>
+        <v>0.7580644445883913</v>
       </c>
       <c r="G18" t="n">
-        <v>22.02151679430591</v>
+        <v>22.79334071801153</v>
       </c>
       <c r="H18" t="n">
-        <v>37.0832876994767</v>
+        <v>36.93177311767128</v>
       </c>
       <c r="I18" t="n">
-        <v>1.626767657014117</v>
+        <v>1.727540335793799</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737164261622823</v>
+        <v>4.737902778677444</v>
       </c>
       <c r="K18" t="n">
-        <v>20.5498644054779</v>
+        <v>19.46804715773721</v>
       </c>
       <c r="L18" t="n">
-        <v>43.41758663923878</v>
+        <v>43.36620706155241</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94581139574936</v>
+        <v>99.94245646886006</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.45420163594892</v>
+        <v>79.57054695044798</v>
       </c>
       <c r="C19" t="n">
-        <v>35.22725783136025</v>
+        <v>36.41326687605459</v>
       </c>
       <c r="D19" t="n">
-        <v>1.26336962031519</v>
+        <v>1.322589729111688</v>
       </c>
       <c r="E19" t="n">
-        <v>11.81837278006705</v>
+        <v>12.14980636470516</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583848620102573</v>
+        <v>0.7585218923134235</v>
       </c>
       <c r="G19" t="n">
-        <v>21.40751456769545</v>
+        <v>22.20432217492978</v>
       </c>
       <c r="H19" t="n">
-        <v>37.10474567650414</v>
+        <v>36.95405929098371</v>
       </c>
       <c r="I19" t="n">
-        <v>1.361908741792716</v>
+        <v>1.44048567144532</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739905387564107</v>
+        <v>4.740761826958896</v>
       </c>
       <c r="K19" t="n">
-        <v>21.54579836405107</v>
+        <v>20.42945304955202</v>
       </c>
       <c r="L19" t="n">
-        <v>43.18157309996</v>
+        <v>43.10929284284356</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95462929537132</v>
+        <v>99.95201276845017</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.70251008310075</v>
+        <v>77.10563371948734</v>
       </c>
       <c r="C20" t="n">
-        <v>32.68510426915544</v>
+        <v>34.17039438446682</v>
       </c>
       <c r="D20" t="n">
-        <v>1.163154176581324</v>
+        <v>1.231850941180342</v>
       </c>
       <c r="E20" t="n">
-        <v>11.07014156619037</v>
+        <v>11.5164170854175</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587640389932665</v>
+        <v>0.7589157269276833</v>
       </c>
       <c r="G20" t="n">
-        <v>19.70938637374256</v>
+        <v>20.68095235234431</v>
       </c>
       <c r="H20" t="n">
-        <v>37.12329729353358</v>
+        <v>36.97324632808004</v>
       </c>
       <c r="I20" t="n">
-        <v>1.135491390351731</v>
+        <v>1.201027992239457</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742275243707915</v>
+        <v>4.74322329329802</v>
       </c>
       <c r="K20" t="n">
-        <v>24.29748991689924</v>
+        <v>22.89436628051266</v>
       </c>
       <c r="L20" t="n">
-        <v>42.97957501556218</v>
+        <v>42.89522584414703</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96216920161686</v>
+        <v>99.95998650912651</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.64694334492998</v>
+        <v>82.64043275171957</v>
       </c>
       <c r="C21" t="n">
-        <v>36.43265057749861</v>
+        <v>37.55401980361756</v>
       </c>
       <c r="D21" t="n">
-        <v>1.163896007788982</v>
+        <v>1.232733914059851</v>
       </c>
       <c r="E21" t="n">
-        <v>13.07417492253876</v>
+        <v>13.35690870078882</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592479600887728</v>
+        <v>0.7594597067082792</v>
       </c>
       <c r="G21" t="n">
-        <v>21.45856753811564</v>
+        <v>22.23183565851739</v>
       </c>
       <c r="H21" t="n">
-        <v>38.88358462321799</v>
+        <v>38.5358077141609</v>
       </c>
       <c r="I21" t="n">
-        <v>1.562172542625011</v>
+        <v>1.777063890557583</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745299750554829</v>
+        <v>4.746623166926745</v>
       </c>
       <c r="K21" t="n">
-        <v>18.35305665507002</v>
+        <v>17.35956724828042</v>
       </c>
       <c r="L21" t="n">
-        <v>45.16225353868771</v>
+        <v>45.0272199137915</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94796077125633</v>
+        <v>99.94080696568949</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_36_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_36_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.71850773357846</v>
+        <v>45.061088248945</v>
       </c>
       <c r="M2" t="n">
-        <v>98.92452006906322</v>
+        <v>101.0723764915261</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.08171204887398</v>
+        <v>88.01962632405741</v>
       </c>
       <c r="C3" t="n">
-        <v>45.927047645345</v>
+        <v>45.93809271607931</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228871335197796</v>
+        <v>2.228703769363038</v>
       </c>
       <c r="E3" t="n">
-        <v>5.708489758060138</v>
+        <v>5.711247286617789</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429571117325987</v>
+        <v>0.7429012564543459</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97196513124817</v>
+        <v>33.97648118492927</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17602713969953</v>
+        <v>34.1734577968999</v>
       </c>
       <c r="I3" t="n">
-        <v>6.609919624607</v>
+        <v>6.5437021769534</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643481948328741</v>
+        <v>4.643132852839662</v>
       </c>
       <c r="K3" t="n">
-        <v>11.91828795112602</v>
+        <v>11.98037367594259</v>
       </c>
       <c r="L3" t="n">
-        <v>48.91741716470547</v>
+        <v>48.84664542707558</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7627527611765</v>
+        <v>106.7651118190975</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.20428161921677</v>
+        <v>87.05321917702548</v>
       </c>
       <c r="C4" t="n">
-        <v>42.69289729888803</v>
+        <v>42.60177387490938</v>
       </c>
       <c r="D4" t="n">
-        <v>2.186811130175195</v>
+        <v>2.181875554310079</v>
       </c>
       <c r="E4" t="n">
-        <v>6.520748379165761</v>
+        <v>6.501995105729098</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7445247107608945</v>
+        <v>0.7444557003377668</v>
       </c>
       <c r="G4" t="n">
-        <v>33.33089276611134</v>
+        <v>33.26258731103621</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24813669500114</v>
+        <v>34.24496221553726</v>
       </c>
       <c r="I4" t="n">
-        <v>5.519888495746843</v>
+        <v>5.464495162964035</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653279442255591</v>
+        <v>4.652848127111042</v>
       </c>
       <c r="K4" t="n">
-        <v>12.79571838078321</v>
+        <v>12.9467808229745</v>
       </c>
       <c r="L4" t="n">
-        <v>44.32777544186744</v>
+        <v>44.26967579720073</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8163911215387</v>
+        <v>99.81823049508462</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.14327278281036</v>
+        <v>85.91877001892156</v>
       </c>
       <c r="C5" t="n">
-        <v>42.4886193297716</v>
+        <v>42.31542217483201</v>
       </c>
       <c r="D5" t="n">
-        <v>2.135419113697199</v>
+        <v>2.12662343225055</v>
       </c>
       <c r="E5" t="n">
-        <v>7.135523172651792</v>
+        <v>7.097644506045168</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458522863612786</v>
+        <v>0.7457732478774036</v>
       </c>
       <c r="G5" t="n">
-        <v>32.54758698966549</v>
+        <v>32.42027138220393</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30920517261881</v>
+        <v>34.30556940236056</v>
       </c>
       <c r="I5" t="n">
-        <v>4.608109258057802</v>
+        <v>4.561805248950183</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661576789757991</v>
+        <v>4.661082799233773</v>
       </c>
       <c r="K5" t="n">
-        <v>13.85672721718964</v>
+        <v>14.08122998107844</v>
       </c>
       <c r="L5" t="n">
-        <v>43.50132321704577</v>
+        <v>43.451556311785</v>
       </c>
       <c r="M5" t="n">
-        <v>99.846669764007</v>
+        <v>99.84820846769544</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.94624189077227</v>
+        <v>84.59976105847248</v>
       </c>
       <c r="C6" t="n">
-        <v>42.00736584506792</v>
+        <v>41.70488767028214</v>
       </c>
       <c r="D6" t="n">
-        <v>2.077424403815033</v>
+        <v>2.062355890253961</v>
       </c>
       <c r="E6" t="n">
-        <v>7.582714351400304</v>
+        <v>7.517684904846768</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469778857319279</v>
+        <v>0.7468919717216852</v>
       </c>
       <c r="G6" t="n">
-        <v>31.66364441711721</v>
+        <v>31.44051581241245</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36098274366868</v>
+        <v>34.35703069919752</v>
       </c>
       <c r="I6" t="n">
-        <v>3.845886303214574</v>
+        <v>3.80720695677957</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668611785824549</v>
+        <v>4.668074823260533</v>
       </c>
       <c r="K6" t="n">
-        <v>15.05375810922772</v>
+        <v>15.40023894152754</v>
       </c>
       <c r="L6" t="n">
-        <v>42.8108730107583</v>
+        <v>42.76815657571949</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87199696505394</v>
+        <v>99.87328318752915</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.6062785128631</v>
+        <v>83.0260435920687</v>
       </c>
       <c r="C7" t="n">
-        <v>41.26494855560178</v>
+        <v>40.72250985682828</v>
       </c>
       <c r="D7" t="n">
-        <v>2.012633618132664</v>
+        <v>1.985764825565617</v>
       </c>
       <c r="E7" t="n">
-        <v>7.881058662732983</v>
+        <v>7.767948848366563</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479335780138429</v>
+        <v>0.7478445506597974</v>
       </c>
       <c r="G7" t="n">
-        <v>30.67611755665254</v>
+        <v>30.27288873514459</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40494458863677</v>
+        <v>34.40084933035067</v>
       </c>
       <c r="I7" t="n">
-        <v>3.209005646107799</v>
+        <v>3.176718860357744</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674584862586517</v>
+        <v>4.674028441623735</v>
       </c>
       <c r="K7" t="n">
-        <v>16.39372148713688</v>
+        <v>16.97395640793128</v>
       </c>
       <c r="L7" t="n">
-        <v>42.23449978217204</v>
+        <v>42.19777798644103</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89316982491071</v>
+        <v>99.89424425120059</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.39544953994724</v>
+        <v>87.96977065993981</v>
       </c>
       <c r="C8" t="n">
-        <v>43.51877317577306</v>
+        <v>43.07124777274124</v>
       </c>
       <c r="D8" t="n">
-        <v>2.01690046611494</v>
+        <v>1.99001450322486</v>
       </c>
       <c r="E8" t="n">
-        <v>9.680566095209432</v>
+        <v>9.632819484290611</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495192212474014</v>
+        <v>0.7494449910737928</v>
       </c>
       <c r="G8" t="n">
-        <v>31.16404859158495</v>
+        <v>30.7911443212129</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47788417738046</v>
+        <v>34.47446958939447</v>
       </c>
       <c r="I8" t="n">
-        <v>5.622035855613796</v>
+        <v>5.64784657653198</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684495132796259</v>
+        <v>4.684031194211206</v>
       </c>
       <c r="K8" t="n">
-        <v>11.60455046005277</v>
+        <v>12.03022934006019</v>
       </c>
       <c r="L8" t="n">
-        <v>44.68967162504671</v>
+        <v>44.71066336735262</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81299526087255</v>
+        <v>99.81214048015404</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.51457887929963</v>
+        <v>85.98856763096339</v>
       </c>
       <c r="C9" t="n">
-        <v>42.5110020267888</v>
+        <v>41.96664340645518</v>
       </c>
       <c r="D9" t="n">
-        <v>1.931881063858764</v>
+        <v>1.900526239368549</v>
       </c>
       <c r="E9" t="n">
-        <v>10.05474676288531</v>
+        <v>9.985501523001169</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508746267400324</v>
+        <v>0.7508148395244019</v>
       </c>
       <c r="G9" t="n">
-        <v>29.85037504762336</v>
+        <v>29.40650815751198</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54023283004148</v>
+        <v>34.53748261812248</v>
       </c>
       <c r="I9" t="n">
-        <v>4.693502131025483</v>
+        <v>4.715141506407293</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692966417125201</v>
+        <v>4.692592747027513</v>
       </c>
       <c r="K9" t="n">
-        <v>13.48542112070038</v>
+        <v>14.01143236903662</v>
       </c>
       <c r="L9" t="n">
-        <v>43.84740918985488</v>
+        <v>43.86503959738233</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84383233734405</v>
+        <v>99.84311537287412</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.51632057043726</v>
+        <v>83.80374977549235</v>
       </c>
       <c r="C10" t="n">
-        <v>41.24149448822085</v>
+        <v>40.51341366871387</v>
       </c>
       <c r="D10" t="n">
-        <v>1.84245091093947</v>
+        <v>1.802785583331218</v>
       </c>
       <c r="E10" t="n">
-        <v>10.24217738532444</v>
+        <v>10.12787096230785</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520347171237601</v>
+        <v>0.7519901183517372</v>
       </c>
       <c r="G10" t="n">
-        <v>28.46854898433815</v>
+        <v>27.89418418137088</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59359698769296</v>
+        <v>34.59154544417991</v>
       </c>
       <c r="I10" t="n">
-        <v>3.917294602994976</v>
+        <v>3.935435246252405</v>
       </c>
       <c r="J10" t="n">
-        <v>4.7002169820235</v>
+        <v>4.699938239698359</v>
       </c>
       <c r="K10" t="n">
-        <v>15.48367942956276</v>
+        <v>16.19625022450765</v>
       </c>
       <c r="L10" t="n">
-        <v>43.14445102302125</v>
+        <v>43.15935995382274</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86962494080485</v>
+        <v>99.86902384704425</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.4336572766521</v>
+        <v>81.52112047708826</v>
       </c>
       <c r="C11" t="n">
-        <v>39.76661739880111</v>
+        <v>38.84078977560375</v>
       </c>
       <c r="D11" t="n">
-        <v>1.750139563360478</v>
+        <v>1.701737809375104</v>
       </c>
       <c r="E11" t="n">
-        <v>10.2738067897569</v>
+        <v>10.10751674328389</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530287270227232</v>
+        <v>0.7529998710717468</v>
       </c>
       <c r="G11" t="n">
-        <v>27.0422042688511</v>
+        <v>26.33068975146699</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63932144304526</v>
+        <v>34.63799406930035</v>
       </c>
       <c r="I11" t="n">
-        <v>3.26872694072363</v>
+        <v>3.283933038391749</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706429543892019</v>
+        <v>4.70624919419842</v>
       </c>
       <c r="K11" t="n">
-        <v>17.56634272334789</v>
+        <v>18.47887952291174</v>
       </c>
       <c r="L11" t="n">
-        <v>42.55822613887894</v>
+        <v>42.57101305575528</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89118626102794</v>
+        <v>99.89068235427078</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.28751300900356</v>
+        <v>79.13824178655189</v>
       </c>
       <c r="C12" t="n">
-        <v>38.12702493422093</v>
+        <v>36.96616729554909</v>
       </c>
       <c r="D12" t="n">
-        <v>1.655866253888302</v>
+        <v>1.597259031566142</v>
       </c>
       <c r="E12" t="n">
-        <v>10.17490005649608</v>
+        <v>9.94359043114423</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538812991033385</v>
+        <v>0.7538688338703583</v>
       </c>
       <c r="G12" t="n">
-        <v>25.58554438570891</v>
+        <v>24.7141080025368</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67853975875357</v>
+        <v>34.67796635803649</v>
       </c>
       <c r="I12" t="n">
-        <v>2.727023135657492</v>
+        <v>2.73976891770814</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711758119395865</v>
+        <v>4.711680211689742</v>
       </c>
       <c r="K12" t="n">
-        <v>19.71248699099644</v>
+        <v>20.86175821344812</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06969010420698</v>
+        <v>42.08085412882523</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90920202942435</v>
+        <v>99.90877963782243</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>78.01755098765538</v>
+        <v>76.57429216479329</v>
       </c>
       <c r="C13" t="n">
-        <v>36.27898318713423</v>
+        <v>34.82540013815174</v>
       </c>
       <c r="D13" t="n">
-        <v>1.556920316067769</v>
+        <v>1.485777581488631</v>
       </c>
       <c r="E13" t="n">
-        <v>9.946022374103389</v>
+        <v>9.630474857681691</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546139867323324</v>
+        <v>0.7546188249149194</v>
       </c>
       <c r="G13" t="n">
-        <v>24.05668559174039</v>
+        <v>22.98917513751895</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71224338968729</v>
+        <v>34.7124659460863</v>
       </c>
       <c r="I13" t="n">
-        <v>2.274727912247148</v>
+        <v>2.285412161384561</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716337417077077</v>
+        <v>4.716367655718249</v>
       </c>
       <c r="K13" t="n">
-        <v>21.98244901234461</v>
+        <v>23.42570783520671</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66281715786401</v>
+        <v>41.672787334483</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92424935734286</v>
+        <v>99.92389530784145</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.37787093383332</v>
+        <v>83.47166871542831</v>
       </c>
       <c r="C14" t="n">
-        <v>40.18711889720198</v>
+        <v>39.14598909026403</v>
       </c>
       <c r="D14" t="n">
-        <v>1.558751933181826</v>
+        <v>1.487499517666671</v>
       </c>
       <c r="E14" t="n">
-        <v>12.14460255606006</v>
+        <v>12.02893891047028</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555017417949015</v>
+        <v>0.7554933874816456</v>
       </c>
       <c r="G14" t="n">
-        <v>25.77554023970388</v>
+        <v>24.91942536720485</v>
       </c>
       <c r="H14" t="n">
-        <v>36.44363361947929</v>
+        <v>36.65630283828512</v>
       </c>
       <c r="I14" t="n">
-        <v>2.977954957395248</v>
+        <v>2.902175022559441</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721885886218134</v>
+        <v>4.721833671760288</v>
       </c>
       <c r="K14" t="n">
-        <v>15.62212906616667</v>
+        <v>16.52833128457168</v>
       </c>
       <c r="L14" t="n">
-        <v>44.09160351327739</v>
+        <v>44.22905244344395</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90085147664604</v>
+        <v>99.90337281827968</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.67738412937619</v>
+        <v>82.65664140631669</v>
       </c>
       <c r="C15" t="n">
-        <v>39.9475145214773</v>
+        <v>38.76434972817305</v>
       </c>
       <c r="D15" t="n">
-        <v>1.532609585436146</v>
+        <v>1.455628477893787</v>
       </c>
       <c r="E15" t="n">
-        <v>12.35493551960812</v>
+        <v>12.18975596413339</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562493473876697</v>
+        <v>0.7562309482214975</v>
       </c>
       <c r="G15" t="n">
-        <v>25.3432500709253</v>
+        <v>24.40057856388206</v>
       </c>
       <c r="H15" t="n">
-        <v>36.47969636137316</v>
+        <v>36.70716376699326</v>
       </c>
       <c r="I15" t="n">
-        <v>2.48408482347286</v>
+        <v>2.420840258808345</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726558421172935</v>
+        <v>4.726443426384362</v>
       </c>
       <c r="K15" t="n">
-        <v>16.32261587062381</v>
+        <v>17.3433585936833</v>
       </c>
       <c r="L15" t="n">
-        <v>43.64714863686012</v>
+        <v>43.81167570529476</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91727902896123</v>
+        <v>99.91938402715111</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.31068493874841</v>
+        <v>80.08281308504691</v>
       </c>
       <c r="C16" t="n">
-        <v>37.96535711376735</v>
+        <v>36.56459344658434</v>
       </c>
       <c r="D16" t="n">
-        <v>1.441374135530265</v>
+        <v>1.358295048109192</v>
       </c>
       <c r="E16" t="n">
-        <v>11.9647574625261</v>
+        <v>11.71117460065324</v>
       </c>
       <c r="F16" t="n">
-        <v>0.756891665286455</v>
+        <v>0.7568664892449853</v>
       </c>
       <c r="G16" t="n">
-        <v>23.83457960176592</v>
+        <v>22.76898641216242</v>
       </c>
       <c r="H16" t="n">
-        <v>36.51068027163517</v>
+        <v>36.73801268753093</v>
       </c>
       <c r="I16" t="n">
-        <v>2.071828893964168</v>
+        <v>2.019062289564983</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730572908040344</v>
+        <v>4.730415557781162</v>
       </c>
       <c r="K16" t="n">
-        <v>18.6893150612516</v>
+        <v>19.91718691495308</v>
       </c>
       <c r="L16" t="n">
-        <v>43.27632546877348</v>
+        <v>43.45097407571792</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93099764379241</v>
+        <v>99.93275443725534</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.8145358895907</v>
+        <v>81.88883616177934</v>
       </c>
       <c r="C17" t="n">
-        <v>39.07048996967661</v>
+        <v>37.87845370423589</v>
       </c>
       <c r="D17" t="n">
-        <v>1.442575978997398</v>
+        <v>1.359401979653666</v>
       </c>
       <c r="E17" t="n">
-        <v>12.68425533264711</v>
+        <v>12.5296435521167</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575227750592952</v>
+        <v>0.7574832914582208</v>
       </c>
       <c r="G17" t="n">
-        <v>24.2187135544949</v>
+        <v>23.26279361996021</v>
       </c>
       <c r="H17" t="n">
-        <v>36.9053837832339</v>
+        <v>37.24320384011399</v>
       </c>
       <c r="I17" t="n">
-        <v>2.071567121037496</v>
+        <v>2.002039306862672</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734517344120595</v>
+        <v>4.734270571613883</v>
       </c>
       <c r="K17" t="n">
-        <v>17.18546411040929</v>
+        <v>18.11116383822065</v>
       </c>
       <c r="L17" t="n">
-        <v>43.67505121156482</v>
+        <v>43.94370215455404</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93100529165073</v>
+        <v>99.93331969701057</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.5319528422628</v>
+        <v>79.38395598177881</v>
       </c>
       <c r="C18" t="n">
-        <v>37.10820224957045</v>
+        <v>35.68250327803031</v>
       </c>
       <c r="D18" t="n">
-        <v>1.357674334225904</v>
+        <v>1.268636061982829</v>
       </c>
       <c r="E18" t="n">
-        <v>12.22565711329445</v>
+        <v>11.97130766451586</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580644445883913</v>
+        <v>0.7580143162161207</v>
       </c>
       <c r="G18" t="n">
-        <v>22.79334071801153</v>
+        <v>21.70956003482086</v>
       </c>
       <c r="H18" t="n">
-        <v>36.93177311767128</v>
+        <v>37.26931275040367</v>
       </c>
       <c r="I18" t="n">
-        <v>1.727540335793799</v>
+        <v>1.669535677488721</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737902778677444</v>
+        <v>4.737589476350758</v>
       </c>
       <c r="K18" t="n">
-        <v>19.46804715773721</v>
+        <v>20.61604401822117</v>
       </c>
       <c r="L18" t="n">
-        <v>43.36620706155241</v>
+        <v>43.6458405007801</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94245646886006</v>
+        <v>99.9443877970316</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.57054695044798</v>
+        <v>78.3508137852147</v>
       </c>
       <c r="C19" t="n">
-        <v>36.41326687605459</v>
+        <v>34.9062558361783</v>
       </c>
       <c r="D19" t="n">
-        <v>1.322589729111688</v>
+        <v>1.231863056421001</v>
       </c>
       <c r="E19" t="n">
-        <v>12.14980636470516</v>
+        <v>11.85632160126822</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585218923134235</v>
+        <v>0.7584632520124605</v>
       </c>
       <c r="G19" t="n">
-        <v>22.20432217492978</v>
+        <v>21.08028124019354</v>
       </c>
       <c r="H19" t="n">
-        <v>36.95405929098371</v>
+        <v>37.29138559024416</v>
       </c>
       <c r="I19" t="n">
-        <v>1.44048567144532</v>
+        <v>1.392103719997428</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740761826958896</v>
+        <v>4.740395325077881</v>
       </c>
       <c r="K19" t="n">
-        <v>20.42945304955202</v>
+        <v>21.6491862147853</v>
       </c>
       <c r="L19" t="n">
-        <v>43.10929284284356</v>
+        <v>43.39818195799503</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95201276845017</v>
+        <v>99.95362400895863</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.10563371948734</v>
+        <v>75.56823644959091</v>
       </c>
       <c r="C20" t="n">
-        <v>34.17039438446682</v>
+        <v>32.33769955315998</v>
       </c>
       <c r="D20" t="n">
-        <v>1.231850941180342</v>
+        <v>1.13212315208864</v>
       </c>
       <c r="E20" t="n">
-        <v>11.5164170854175</v>
+        <v>11.08980092459479</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589157269276833</v>
+        <v>0.7588515692260287</v>
       </c>
       <c r="G20" t="n">
-        <v>20.68095235234431</v>
+        <v>19.37348012846542</v>
       </c>
       <c r="H20" t="n">
-        <v>36.97324632808004</v>
+        <v>37.310477994397</v>
       </c>
       <c r="I20" t="n">
-        <v>1.201027992239457</v>
+        <v>1.160680373156348</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74322329329802</v>
+        <v>4.742822307662683</v>
       </c>
       <c r="K20" t="n">
-        <v>22.89436628051266</v>
+        <v>24.43176355040908</v>
       </c>
       <c r="L20" t="n">
-        <v>42.89522584414703</v>
+        <v>43.19186734865323</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95998650912651</v>
+        <v>99.9613304522223</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.64043275171957</v>
+        <v>81.63984530902826</v>
       </c>
       <c r="C21" t="n">
-        <v>37.55401980361756</v>
+        <v>36.13349292372612</v>
       </c>
       <c r="D21" t="n">
-        <v>1.232733914059851</v>
+        <v>1.132884385731432</v>
       </c>
       <c r="E21" t="n">
-        <v>13.35690870078882</v>
+        <v>13.12538229720967</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594597067082792</v>
+        <v>0.7593618170231121</v>
       </c>
       <c r="G21" t="n">
-        <v>22.23183565851739</v>
+        <v>21.14016039403191</v>
       </c>
       <c r="H21" t="n">
-        <v>38.5358077141609</v>
+        <v>39.08921900282619</v>
       </c>
       <c r="I21" t="n">
-        <v>1.777063890557583</v>
+        <v>1.646826055811505</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746623166926745</v>
+        <v>4.746011356394455</v>
       </c>
       <c r="K21" t="n">
-        <v>17.35956724828042</v>
+        <v>18.36015469097173</v>
       </c>
       <c r="L21" t="n">
-        <v>45.0272199137915</v>
+        <v>45.45149506921209</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94080696568949</v>
+        <v>99.94514268390994</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_36_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_36_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.061088248945</v>
+        <v>43.40052959531105</v>
       </c>
       <c r="M2" t="n">
-        <v>101.0723764915261</v>
+        <v>96.8812330168517</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.01962632405741</v>
+        <v>81.6063044936767</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93809271607931</v>
+        <v>43.36186004923226</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228703769363038</v>
+        <v>2.186589746474978</v>
       </c>
       <c r="E3" t="n">
-        <v>5.711247286617789</v>
+        <v>4.172097553675173</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429012564543459</v>
+        <v>0.7377241757381499</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97648118492927</v>
+        <v>32.88995410322779</v>
       </c>
       <c r="H3" t="n">
-        <v>34.1734577968999</v>
+        <v>33.93531208395488</v>
       </c>
       <c r="I3" t="n">
-        <v>6.5437021769534</v>
+        <v>3.073850732242291</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643132852839662</v>
+        <v>4.610776098363436</v>
       </c>
       <c r="K3" t="n">
-        <v>11.98037367594259</v>
+        <v>18.3936955063233</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84664542707558</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7651118190975</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.05321917702548</v>
+        <v>88.78793780613987</v>
       </c>
       <c r="C4" t="n">
-        <v>42.60177387490938</v>
+        <v>43.00279906772336</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181875554310079</v>
+        <v>2.192355777567427</v>
       </c>
       <c r="E4" t="n">
-        <v>6.501995105729098</v>
+        <v>6.58958048283858</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444557003377668</v>
+        <v>0.7396695523419756</v>
       </c>
       <c r="G4" t="n">
-        <v>33.26258731103621</v>
+        <v>33.59459151676023</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24496221553726</v>
+        <v>34.02479940773087</v>
       </c>
       <c r="I4" t="n">
-        <v>5.464495162964035</v>
+        <v>7.024006366763451</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652848127111042</v>
+        <v>4.622934702137347</v>
       </c>
       <c r="K4" t="n">
-        <v>12.9467808229745</v>
+        <v>11.21206219386012</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26967579720073</v>
+        <v>45.55162097854239</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81823049508462</v>
+        <v>99.76648224012587</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.91877001892156</v>
+        <v>87.6801400581582</v>
       </c>
       <c r="C5" t="n">
-        <v>42.31542217483201</v>
+        <v>42.9839560213548</v>
       </c>
       <c r="D5" t="n">
-        <v>2.12662343225055</v>
+        <v>2.139805328857229</v>
       </c>
       <c r="E5" t="n">
-        <v>7.097644506045168</v>
+        <v>7.409361348395692</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457732478774036</v>
+        <v>0.7413191817820656</v>
       </c>
       <c r="G5" t="n">
-        <v>32.42027138220393</v>
+        <v>32.78933405056538</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30556940236056</v>
+        <v>34.100682361975</v>
       </c>
       <c r="I5" t="n">
-        <v>4.561805248950183</v>
+        <v>5.866392900444937</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661082799233773</v>
+        <v>4.633244886137909</v>
       </c>
       <c r="K5" t="n">
-        <v>14.08122998107844</v>
+        <v>12.31985994184179</v>
       </c>
       <c r="L5" t="n">
-        <v>43.451556311785</v>
+        <v>44.50107274883776</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84820846769544</v>
+        <v>99.80488871203434</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.59976105847248</v>
+        <v>86.39731806483985</v>
       </c>
       <c r="C6" t="n">
-        <v>41.70488767028214</v>
+        <v>42.61177470801048</v>
       </c>
       <c r="D6" t="n">
-        <v>2.062355890253961</v>
+        <v>2.078892006356782</v>
       </c>
       <c r="E6" t="n">
-        <v>7.517684904846768</v>
+        <v>8.014757304114019</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468919717216852</v>
+        <v>0.7427200378807763</v>
       </c>
       <c r="G6" t="n">
-        <v>31.44051581241245</v>
+        <v>31.8559279819565</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35703069919752</v>
+        <v>34.16512174251569</v>
       </c>
       <c r="I6" t="n">
-        <v>3.80720695677957</v>
+        <v>4.897898755261227</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668074823260533</v>
+        <v>4.642000236754851</v>
       </c>
       <c r="K6" t="n">
-        <v>15.40023894152754</v>
+        <v>13.60268193516014</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76815657571949</v>
+        <v>43.6225879984837</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87328318752915</v>
+        <v>99.83704464165432</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.0260435920687</v>
+        <v>84.86664019582898</v>
       </c>
       <c r="C7" t="n">
-        <v>40.72250985682828</v>
+        <v>41.84188317730572</v>
       </c>
       <c r="D7" t="n">
-        <v>1.985764825565617</v>
+        <v>2.006252615053184</v>
       </c>
       <c r="E7" t="n">
-        <v>7.767948848366563</v>
+        <v>8.416066507983908</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478445506597974</v>
+        <v>0.7439126307993731</v>
       </c>
       <c r="G7" t="n">
-        <v>30.27288873514459</v>
+        <v>30.74283734956921</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40084933035067</v>
+        <v>34.21998101677114</v>
       </c>
       <c r="I7" t="n">
-        <v>3.176718860357744</v>
+        <v>4.08813613315609</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674028441623735</v>
+        <v>4.649453942496081</v>
       </c>
       <c r="K7" t="n">
-        <v>16.97395640793128</v>
+        <v>15.133359804171</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19777798644103</v>
+        <v>42.88870427532157</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89424425120059</v>
+        <v>99.8639472567983</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.96977065993981</v>
+        <v>83.09628458212016</v>
       </c>
       <c r="C8" t="n">
-        <v>43.07124777274124</v>
+        <v>40.7065101748574</v>
       </c>
       <c r="D8" t="n">
-        <v>1.99001450322486</v>
+        <v>1.922598801547754</v>
       </c>
       <c r="E8" t="n">
-        <v>9.632819484290611</v>
+        <v>8.633719263377499</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494449910737928</v>
+        <v>0.7449306526215524</v>
       </c>
       <c r="G8" t="n">
-        <v>30.7911443212129</v>
+        <v>29.46096707910954</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47446958939447</v>
+        <v>34.26681002059139</v>
       </c>
       <c r="I8" t="n">
-        <v>5.64784657653198</v>
+        <v>3.41144218598773</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684031194211206</v>
+        <v>4.655816578884702</v>
       </c>
       <c r="K8" t="n">
-        <v>12.03022934006019</v>
+        <v>16.90371541787984</v>
       </c>
       <c r="L8" t="n">
-        <v>44.71066336735262</v>
+        <v>42.27621507023063</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81214048015404</v>
+        <v>99.88644066296787</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.98856763096339</v>
+        <v>81.06187729971003</v>
       </c>
       <c r="C9" t="n">
-        <v>41.96664340645518</v>
+        <v>39.20161992896672</v>
       </c>
       <c r="D9" t="n">
-        <v>1.900526239368549</v>
+        <v>1.826993089661405</v>
       </c>
       <c r="E9" t="n">
-        <v>9.985501523001169</v>
+        <v>8.678753379865817</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508148395244019</v>
+        <v>0.745802504474775</v>
       </c>
       <c r="G9" t="n">
-        <v>29.40650815751198</v>
+        <v>27.99595174247711</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53748261812248</v>
+        <v>34.30691520583964</v>
       </c>
       <c r="I9" t="n">
-        <v>4.715141506407293</v>
+        <v>2.846195724423932</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692592747027513</v>
+        <v>4.661265652967344</v>
       </c>
       <c r="K9" t="n">
-        <v>14.01143236903662</v>
+        <v>18.93812270028998</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86503959738233</v>
+        <v>41.7654950877992</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84311537287412</v>
+        <v>99.9052377170559</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.80374977549235</v>
+        <v>85.81350023670753</v>
       </c>
       <c r="C10" t="n">
-        <v>40.51341366871387</v>
+        <v>42.48027898959616</v>
       </c>
       <c r="D10" t="n">
-        <v>1.802785583331218</v>
+        <v>1.82904871724476</v>
       </c>
       <c r="E10" t="n">
-        <v>10.12787096230785</v>
+        <v>10.5481070606384</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519901183517372</v>
+        <v>0.7466416385736444</v>
       </c>
       <c r="G10" t="n">
-        <v>27.89418418137088</v>
+        <v>29.40427794069749</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59154544417991</v>
+        <v>35.72234213730648</v>
       </c>
       <c r="I10" t="n">
-        <v>3.935435246252405</v>
+        <v>2.896572501161468</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699938239698359</v>
+        <v>4.666510241085278</v>
       </c>
       <c r="K10" t="n">
-        <v>16.19625022450765</v>
+        <v>14.18649976329247</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15935995382274</v>
+        <v>43.23677734354135</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86902384704425</v>
+        <v>99.90355609642998</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.52112047708826</v>
+        <v>85.33340597437675</v>
       </c>
       <c r="C11" t="n">
-        <v>38.84078977560375</v>
+        <v>42.34241248396874</v>
       </c>
       <c r="D11" t="n">
-        <v>1.701737809375104</v>
+        <v>1.800481127412046</v>
       </c>
       <c r="E11" t="n">
-        <v>10.10751674328389</v>
+        <v>10.84315729314494</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529998710717468</v>
+        <v>0.7473634407818607</v>
       </c>
       <c r="G11" t="n">
-        <v>26.33068975146699</v>
+        <v>28.99234437887007</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63799406930035</v>
+        <v>35.80420273853911</v>
       </c>
       <c r="I11" t="n">
-        <v>3.283933038391749</v>
+        <v>2.474835490742093</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70624919419842</v>
+        <v>4.67102150488663</v>
       </c>
       <c r="K11" t="n">
-        <v>18.47887952291174</v>
+        <v>14.66659402562325</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57101305575528</v>
+        <v>42.90857864709898</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89068235427078</v>
+        <v>99.91758515669099</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.13824178655189</v>
+        <v>83.15986564455953</v>
       </c>
       <c r="C12" t="n">
-        <v>36.96616729554909</v>
+        <v>40.55353306188364</v>
       </c>
       <c r="D12" t="n">
-        <v>1.597259031566142</v>
+        <v>1.707901735032265</v>
       </c>
       <c r="E12" t="n">
-        <v>9.94359043114423</v>
+        <v>10.62962179253153</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538688338703583</v>
+        <v>0.7479817718525378</v>
       </c>
       <c r="G12" t="n">
-        <v>24.7141080025368</v>
+        <v>27.50157972413627</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67796635803649</v>
+        <v>35.83382534222294</v>
       </c>
       <c r="I12" t="n">
-        <v>2.73976891770814</v>
+        <v>2.064069204705631</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711680211689742</v>
+        <v>4.674886074078362</v>
       </c>
       <c r="K12" t="n">
-        <v>20.86175821344812</v>
+        <v>16.84013435544048</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08085412882523</v>
+        <v>42.53758715237748</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90877963782243</v>
+        <v>99.93125456970159</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.57429216479329</v>
+        <v>84.15068469759355</v>
       </c>
       <c r="C13" t="n">
-        <v>34.82540013815174</v>
+        <v>41.41520143315305</v>
       </c>
       <c r="D13" t="n">
-        <v>1.485777581488631</v>
+        <v>1.709193602459035</v>
       </c>
       <c r="E13" t="n">
-        <v>9.630474857681691</v>
+        <v>11.21116374996575</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546188249149194</v>
+        <v>0.7485475498871011</v>
       </c>
       <c r="G13" t="n">
-        <v>22.98917513751895</v>
+        <v>27.77762324514045</v>
       </c>
       <c r="H13" t="n">
-        <v>34.7124659460863</v>
+        <v>36.11617142530376</v>
       </c>
       <c r="I13" t="n">
-        <v>2.285412161384561</v>
+        <v>1.909562938043081</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716367655718249</v>
+        <v>4.678422186794383</v>
       </c>
       <c r="K13" t="n">
-        <v>23.42570783520671</v>
+        <v>15.84931530240642</v>
       </c>
       <c r="L13" t="n">
-        <v>41.672787334483</v>
+        <v>42.67187927695495</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92389530784145</v>
+        <v>99.93639601251444</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.47166871542831</v>
+        <v>81.88830601801905</v>
       </c>
       <c r="C14" t="n">
-        <v>39.14598909026403</v>
+        <v>39.44936654260601</v>
       </c>
       <c r="D14" t="n">
-        <v>1.487499517666671</v>
+        <v>1.615226724962563</v>
       </c>
       <c r="E14" t="n">
-        <v>12.02893891047028</v>
+        <v>10.86019303440498</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554933874816456</v>
+        <v>0.7490327382647299</v>
       </c>
       <c r="G14" t="n">
-        <v>24.91942536720485</v>
+        <v>26.25048406274239</v>
       </c>
       <c r="H14" t="n">
-        <v>36.65630283828512</v>
+        <v>36.13958095569719</v>
       </c>
       <c r="I14" t="n">
-        <v>2.902175022559441</v>
+        <v>1.592333887792631</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721833671760288</v>
+        <v>4.681454614154563</v>
       </c>
       <c r="K14" t="n">
-        <v>16.52833128457168</v>
+        <v>18.11169398198095</v>
       </c>
       <c r="L14" t="n">
-        <v>44.22905244344395</v>
+        <v>42.38589606046738</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90337281827968</v>
+        <v>99.94695658505435</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.65664140631669</v>
+        <v>80.79187054696214</v>
       </c>
       <c r="C15" t="n">
-        <v>38.76434972817305</v>
+        <v>38.57087291292179</v>
       </c>
       <c r="D15" t="n">
-        <v>1.455628477893787</v>
+        <v>1.568978003150303</v>
       </c>
       <c r="E15" t="n">
-        <v>12.18975596413339</v>
+        <v>10.77516018298467</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562309482214975</v>
+        <v>0.7494516577245376</v>
       </c>
       <c r="G15" t="n">
-        <v>24.40057856388206</v>
+        <v>25.49885500900501</v>
       </c>
       <c r="H15" t="n">
-        <v>36.70716376699326</v>
+        <v>36.15979312127851</v>
       </c>
       <c r="I15" t="n">
-        <v>2.420840258808345</v>
+        <v>1.355559712040749</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726443426384362</v>
+        <v>4.684072860778361</v>
       </c>
       <c r="K15" t="n">
-        <v>17.3433585936833</v>
+        <v>19.20812945303786</v>
       </c>
       <c r="L15" t="n">
-        <v>43.81167570529476</v>
+        <v>42.17583756745361</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91938402715111</v>
+        <v>99.95483993341327</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.08281308504691</v>
+        <v>78.23274880630196</v>
       </c>
       <c r="C16" t="n">
-        <v>36.56459344658434</v>
+        <v>36.22159529443225</v>
       </c>
       <c r="D16" t="n">
-        <v>1.358295048109192</v>
+        <v>1.463580748632691</v>
       </c>
       <c r="E16" t="n">
-        <v>11.71117460065324</v>
+        <v>10.23969369448071</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568664892449853</v>
+        <v>0.7498125522287545</v>
       </c>
       <c r="G16" t="n">
-        <v>22.76898641216242</v>
+        <v>23.78595061780538</v>
       </c>
       <c r="H16" t="n">
-        <v>36.73801268753093</v>
+        <v>36.17720567948235</v>
       </c>
       <c r="I16" t="n">
-        <v>2.019062289564983</v>
+        <v>1.130177062242369</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730415557781162</v>
+        <v>4.686328451429717</v>
       </c>
       <c r="K16" t="n">
-        <v>19.91718691495308</v>
+        <v>21.76725119369802</v>
       </c>
       <c r="L16" t="n">
-        <v>43.45097407571792</v>
+        <v>41.97349907542416</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93275443725534</v>
+        <v>99.96234556355444</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.88883616177934</v>
+        <v>83.30688236327049</v>
       </c>
       <c r="C17" t="n">
-        <v>37.87845370423589</v>
+        <v>39.58711102154661</v>
       </c>
       <c r="D17" t="n">
-        <v>1.359401979653666</v>
+        <v>1.464309867586607</v>
       </c>
       <c r="E17" t="n">
-        <v>12.5296435521167</v>
+        <v>12.02341897862527</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574832914582208</v>
+        <v>0.7501860898994469</v>
       </c>
       <c r="G17" t="n">
-        <v>23.26279361996021</v>
+        <v>25.36891738404049</v>
       </c>
       <c r="H17" t="n">
-        <v>37.24320384011399</v>
+        <v>37.76634545594372</v>
       </c>
       <c r="I17" t="n">
-        <v>2.002039306862672</v>
+        <v>1.245041525303406</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734270571613883</v>
+        <v>4.688663061871545</v>
       </c>
       <c r="K17" t="n">
-        <v>18.11116383822065</v>
+        <v>16.69311763672951</v>
       </c>
       <c r="L17" t="n">
-        <v>43.94370215455404</v>
+        <v>43.67829062219361</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93331969701057</v>
+        <v>99.95851928046974</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.38395598177881</v>
+        <v>84.87897459703501</v>
       </c>
       <c r="C18" t="n">
-        <v>35.68250327803031</v>
+        <v>40.30922063136061</v>
       </c>
       <c r="D18" t="n">
-        <v>1.268636061982829</v>
+        <v>1.465487686311115</v>
       </c>
       <c r="E18" t="n">
-        <v>11.97130766451586</v>
+        <v>12.61551298635547</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580143162161207</v>
+        <v>0.7507895026354446</v>
       </c>
       <c r="G18" t="n">
-        <v>21.70956003482086</v>
+        <v>25.50985320747266</v>
       </c>
       <c r="H18" t="n">
-        <v>37.26931275040367</v>
+        <v>37.79672284383059</v>
       </c>
       <c r="I18" t="n">
-        <v>1.669535677488721</v>
+        <v>2.048173978958183</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737589476350758</v>
+        <v>4.692434391471531</v>
       </c>
       <c r="K18" t="n">
-        <v>20.61604401822117</v>
+        <v>15.12102540296501</v>
       </c>
       <c r="L18" t="n">
-        <v>43.6458405007801</v>
+        <v>44.50153637058214</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9443877970316</v>
+        <v>99.93178240490778</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.3508137852147</v>
+        <v>82.05046128632949</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9062558361783</v>
+        <v>37.79759868025783</v>
       </c>
       <c r="D19" t="n">
-        <v>1.231863056421001</v>
+        <v>1.361732187459038</v>
       </c>
       <c r="E19" t="n">
-        <v>11.85632160126822</v>
+        <v>12.0070095232405</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584632520124605</v>
+        <v>0.7513104606842302</v>
       </c>
       <c r="G19" t="n">
-        <v>21.08028124019354</v>
+        <v>23.7037735181598</v>
       </c>
       <c r="H19" t="n">
-        <v>37.29138559024416</v>
+        <v>37.82294924539067</v>
       </c>
       <c r="I19" t="n">
-        <v>1.392103719997428</v>
+        <v>1.707995972118828</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740395325077881</v>
+        <v>4.695690379276441</v>
       </c>
       <c r="K19" t="n">
-        <v>21.6491862147853</v>
+        <v>17.9495387136705</v>
       </c>
       <c r="L19" t="n">
-        <v>43.39818195799503</v>
+        <v>44.19596888443394</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95362400895863</v>
+        <v>99.94310627836227</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.56823644959091</v>
+        <v>79.2660284475447</v>
       </c>
       <c r="C20" t="n">
-        <v>32.33769955315998</v>
+        <v>35.27661451355304</v>
       </c>
       <c r="D20" t="n">
-        <v>1.13212315208864</v>
+        <v>1.260209853295866</v>
       </c>
       <c r="E20" t="n">
-        <v>11.08980092459479</v>
+        <v>11.34920485197333</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588515692260287</v>
+        <v>0.751760423578037</v>
       </c>
       <c r="G20" t="n">
-        <v>19.37348012846542</v>
+        <v>21.93656669276401</v>
       </c>
       <c r="H20" t="n">
-        <v>37.310477994397</v>
+        <v>37.84560156368697</v>
       </c>
       <c r="I20" t="n">
-        <v>1.160680373156348</v>
+        <v>1.424182414883754</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742822307662683</v>
+        <v>4.698502647362734</v>
       </c>
       <c r="K20" t="n">
-        <v>24.43176355040908</v>
+        <v>20.7339715524553</v>
       </c>
       <c r="L20" t="n">
-        <v>43.19186734865323</v>
+        <v>43.9419696014328</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9613304522223</v>
+        <v>99.95255566744115</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.63984530902826</v>
+        <v>76.57782651873016</v>
       </c>
       <c r="C21" t="n">
-        <v>36.13349292372612</v>
+        <v>32.80734300597501</v>
       </c>
       <c r="D21" t="n">
-        <v>1.132884385731432</v>
+        <v>1.162747073588745</v>
       </c>
       <c r="E21" t="n">
-        <v>13.12538229720967</v>
+        <v>10.66937936500562</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593618170231121</v>
+        <v>0.7521489888281297</v>
       </c>
       <c r="G21" t="n">
-        <v>21.14016039403191</v>
+        <v>20.24002483386974</v>
       </c>
       <c r="H21" t="n">
-        <v>39.08921900282619</v>
+        <v>37.86516296273817</v>
       </c>
       <c r="I21" t="n">
-        <v>1.646826055811505</v>
+        <v>1.187432114523942</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746011356394455</v>
+        <v>4.700931180175814</v>
       </c>
       <c r="K21" t="n">
-        <v>18.36015469097173</v>
+        <v>23.42217348126983</v>
       </c>
       <c r="L21" t="n">
-        <v>45.45149506921209</v>
+        <v>43.7309228901195</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94514268390994</v>
+        <v>99.96043937736435</v>
       </c>
     </row>
   </sheetData>
